--- a/data/trans_bre/P05B_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P05B_R-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0,07</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>31,69%</t>
         </is>
       </c>
     </row>
@@ -660,27 +660,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 2,7</t>
+          <t>-0,83; 2,49</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 0,83</t>
+          <t>-0,35; 0,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 0,06</t>
+          <t>-2,14; 0,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 0,41</t>
+          <t>-0,36; 0,4</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-31,79; 212,84</t>
+          <t>-36,92; 185,46</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -690,12 +690,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 83,67</t>
+          <t>-100,0; 34,37</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-91,5; —</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,29</t>
+          <t>0,19</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>72,72%</t>
+          <t>43,92%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,55; 3,67</t>
+          <t>0,62; 3,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 2,2</t>
+          <t>-0,47; 2,21</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 1,65</t>
+          <t>-0,56; 1,62</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 0,94</t>
+          <t>-0,36; 0,82</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>13,33; 214,59</t>
+          <t>14,47; 220,98</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-22,12; 206,47</t>
+          <t>-23,9; 203,39</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-36,68; 227,07</t>
+          <t>-42,47; 255,16</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-53,99; 677,87</t>
+          <t>-60,55; 456,37</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,27</t>
+          <t>-0,18</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-47,06%</t>
+          <t>-30,01%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 3,59</t>
+          <t>-0,28; 3,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 0,16</t>
+          <t>-2,45; 0,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,24; 3,49</t>
+          <t>0,21; 3,4</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 0,26</t>
+          <t>-1,05; 0,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-11,13; 239,71</t>
+          <t>-13,64; 240,05</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-81,83; 22,75</t>
+          <t>-80,86; 26,12</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,26; 360,2</t>
+          <t>-0,25; 345,05</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-97,87; 169,31</t>
+          <t>-86,52; 260,37</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,21</t>
+          <t>0,45</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>16,5%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,05; 4,06</t>
+          <t>0,07; 3,97</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 0,83</t>
+          <t>-1,95; 0,83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,1; 2,68</t>
+          <t>0,05; 2,58</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 1,72</t>
+          <t>-1,07; 1,8</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,4; 112,2</t>
+          <t>0,27; 110,08</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-58,23; 55,16</t>
+          <t>-59,1; 51,37</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 289,22</t>
+          <t>-3,82; 282,17</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-37,24; 79,64</t>
+          <t>-28,97; 93,88</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,2</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>18,87%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,82; 2,67</t>
+          <t>0,81; 2,62</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 0,62</t>
+          <t>-0,66; 0,61</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,46</t>
+          <t>0,13; 1,39</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 0,65</t>
+          <t>-0,35; 0,64</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>24,44; 108,36</t>
+          <t>23,25; 101,58</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-34,55; 47,56</t>
+          <t>-33,18; 47,75</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,97; 136,62</t>
+          <t>6,54; 127,53</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-27,96; 85,03</t>
+          <t>-26,5; 73,67</t>
         </is>
       </c>
     </row>
